--- a/Project Translation.xlsx
+++ b/Project Translation.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mozart_sk8/Desktop/MPI/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mozart_sk8/software/ClientProjects/geolocation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35B5668F-E6AC-0E42-81AA-E677DC20EE0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD5C7FE-88B0-C546-B37D-7F9F2B933AB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="820" yWindow="500" windowWidth="27600" windowHeight="16940" xr2:uid="{BFCE1D6D-76FF-9F47-800D-D643F1D4128E}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="164">
   <si>
     <t>Module</t>
   </si>
@@ -521,6 +521,15 @@
   </si>
   <si>
     <t>Target(s)</t>
+  </si>
+  <si>
+    <t>Label Division</t>
+  </si>
+  <si>
+    <t>Division</t>
+  </si>
+  <si>
+    <t>ພະແນກ</t>
   </si>
 </sst>
 </file>
@@ -913,7 +922,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85379C79-D204-7744-BFD4-26257222829D}">
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.1640625" customWidth="1"/>
@@ -1436,6 +1445,17 @@
       </c>
       <c r="C47" t="s">
         <v>158</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>161</v>
+      </c>
+      <c r="B48" t="s">
+        <v>162</v>
+      </c>
+      <c r="C48" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/Project Translation.xlsx
+++ b/Project Translation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mozart_sk8/software/ClientProjects/geolocation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD5C7FE-88B0-C546-B37D-7F9F2B933AB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5BF4BE7-0CAA-0E49-93ED-C5737E42D926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="820" yWindow="500" windowWidth="27600" windowHeight="16940" xr2:uid="{BFCE1D6D-76FF-9F47-800D-D643F1D4128E}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="173">
   <si>
     <t>Module</t>
   </si>
@@ -530,6 +530,33 @@
   </si>
   <si>
     <t>ພະແນກ</t>
+  </si>
+  <si>
+    <t>Label Dashboard</t>
+  </si>
+  <si>
+    <t>Dashboard</t>
+  </si>
+  <si>
+    <t>ຫນ້າຈໍຫຼັກ</t>
+  </si>
+  <si>
+    <t>Label Demographics</t>
+  </si>
+  <si>
+    <t>Demographics</t>
+  </si>
+  <si>
+    <t>ຂໍ້ມູນປະຊາກອນ</t>
+  </si>
+  <si>
+    <t>Label MinistryArea</t>
+  </si>
+  <si>
+    <t>Line Ministry / Area</t>
+  </si>
+  <si>
+    <t>ກະຊວງຮັບຜິດຊອບ / ຂະຫນາດ</t>
   </si>
 </sst>
 </file>
@@ -922,7 +949,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85379C79-D204-7744-BFD4-26257222829D}">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.1640625" customWidth="1"/>
@@ -1456,6 +1483,39 @@
       </c>
       <c r="C48" t="s">
         <v>163</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>164</v>
+      </c>
+      <c r="B49" t="s">
+        <v>165</v>
+      </c>
+      <c r="C49" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>167</v>
+      </c>
+      <c r="B50" t="s">
+        <v>168</v>
+      </c>
+      <c r="C50" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>170</v>
+      </c>
+      <c r="B51" t="s">
+        <v>171</v>
+      </c>
+      <c r="C51" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/Project Translation.xlsx
+++ b/Project Translation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mozart_sk8/software/ClientProjects/geolocation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5BF4BE7-0CAA-0E49-93ED-C5737E42D926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC5F609-36CA-7049-9EDE-671EA1065C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="820" yWindow="500" windowWidth="27600" windowHeight="16940" xr2:uid="{BFCE1D6D-76FF-9F47-800D-D643F1D4128E}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="181">
   <si>
     <t>Module</t>
   </si>
@@ -557,6 +557,30 @@
   </si>
   <si>
     <t>ກະຊວງຮັບຜິດຊອບ / ຂະຫນາດ</t>
+  </si>
+  <si>
+    <t>Label Disburement</t>
+  </si>
+  <si>
+    <t>Disbursement</t>
+  </si>
+  <si>
+    <t>ການຈ່າຍເງິນ</t>
+  </si>
+  <si>
+    <t>Label Reports</t>
+  </si>
+  <si>
+    <t>Reports</t>
+  </si>
+  <si>
+    <t>ບົດລາຍງານ</t>
+  </si>
+  <si>
+    <t>Label Climate Change</t>
+  </si>
+  <si>
+    <t>ການປ່ຽນແປງສະພາບດິນຟ້າອາກາດ</t>
   </si>
 </sst>
 </file>
@@ -949,7 +973,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85379C79-D204-7744-BFD4-26257222829D}">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.1640625" customWidth="1"/>
@@ -1516,6 +1540,39 @@
       </c>
       <c r="C51" t="s">
         <v>172</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>173</v>
+      </c>
+      <c r="B52" t="s">
+        <v>174</v>
+      </c>
+      <c r="C52" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>176</v>
+      </c>
+      <c r="B53" t="s">
+        <v>177</v>
+      </c>
+      <c r="C53" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>179</v>
+      </c>
+      <c r="B54" t="s">
+        <v>54</v>
+      </c>
+      <c r="C54" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/Project Translation.xlsx
+++ b/Project Translation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mozart_sk8/software/ClientProjects/geolocation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC5F609-36CA-7049-9EDE-671EA1065C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58BDEC18-94FE-544F-9CB9-554AF18500B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="820" yWindow="500" windowWidth="27600" windowHeight="16940" xr2:uid="{BFCE1D6D-76FF-9F47-800D-D643F1D4128E}"/>
   </bookViews>
@@ -559,9 +559,6 @@
     <t>ກະຊວງຮັບຜິດຊອບ / ຂະຫນາດ</t>
   </si>
   <si>
-    <t>Label Disburement</t>
-  </si>
-  <si>
     <t>Disbursement</t>
   </si>
   <si>
@@ -581,6 +578,9 @@
   </si>
   <si>
     <t>ການປ່ຽນແປງສະພາບດິນຟ້າອາກາດ</t>
+  </si>
+  <si>
+    <t>Label Disbursement</t>
   </si>
 </sst>
 </file>
@@ -1544,35 +1544,35 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
+        <v>180</v>
+      </c>
+      <c r="B52" t="s">
         <v>173</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>174</v>
-      </c>
-      <c r="C52" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
+        <v>175</v>
+      </c>
+      <c r="B53" t="s">
         <v>176</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
         <v>177</v>
-      </c>
-      <c r="C53" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B54" t="s">
         <v>54</v>
       </c>
       <c r="C54" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/Project Translation.xlsx
+++ b/Project Translation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mozart_sk8/software/ClientProjects/geolocation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58BDEC18-94FE-544F-9CB9-554AF18500B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8AA9482-6FF1-E447-82AE-6956760DACA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="820" yWindow="500" windowWidth="27600" windowHeight="16940" xr2:uid="{BFCE1D6D-76FF-9F47-800D-D643F1D4128E}"/>
   </bookViews>
